--- a/models/linear_regression_metrics.xlsx
+++ b/models/linear_regression_metrics.xlsx
@@ -435,10 +435,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14815.10026817329</v>
+        <v>0.05901716126714377</v>
       </c>
       <c r="C2" t="n">
-        <v>58494.15795571106</v>
+        <v>173980.454570393</v>
       </c>
     </row>
     <row r="3">
@@ -448,10 +448,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>488734539.5874286</v>
+        <v>0.007122101343412747</v>
       </c>
       <c r="C3" t="n">
-        <v>5893847995.102021</v>
+        <v>36058779739.66164</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22107.34130526393</v>
+        <v>0.08439254317422094</v>
       </c>
       <c r="C4" t="n">
-        <v>76771.40089318431</v>
+        <v>189891.4946480269</v>
       </c>
     </row>
     <row r="5">
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9225065922262304</v>
+        <v>0.9547918835848146</v>
       </c>
       <c r="C5" t="n">
-        <v>-20.61552756757056</v>
+        <v>-5.17521499219533</v>
       </c>
     </row>
   </sheetData>

--- a/models/linear_regression_metrics.xlsx
+++ b/models/linear_regression_metrics.xlsx
@@ -438,7 +438,7 @@
         <v>0.05901716126714377</v>
       </c>
       <c r="C2" t="n">
-        <v>173980.454570393</v>
+        <v>175384.2667685635</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +451,7 @@
         <v>0.007122101343412747</v>
       </c>
       <c r="C3" t="n">
-        <v>36058779739.66164</v>
+        <v>36598860976.83069</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>0.08439254317422094</v>
       </c>
       <c r="C4" t="n">
-        <v>189891.4946480269</v>
+        <v>191308.2877891878</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         <v>0.9547918835848146</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.17521499219533</v>
+        <v>-5.267706135180442</v>
       </c>
     </row>
   </sheetData>
